--- a/research/traditional_assets/database/data/czech_republic/czech_republic_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_brokerage_investment_banking.xlsx
@@ -588,100 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>-3.497109826589595</v>
+        <v>-0.3173913043478261</v>
       </c>
       <c r="H2">
-        <v>-3.497109826589595</v>
+        <v>-0.3173913043478261</v>
       </c>
       <c r="I2">
-        <v>-2.658959537572254</v>
+        <v>0.08486956521739131</v>
       </c>
       <c r="J2">
-        <v>-2.155617402887795</v>
+        <v>0.07046147623862488</v>
       </c>
       <c r="K2">
-        <v>5.91</v>
+        <v>10.7</v>
       </c>
       <c r="L2">
-        <v>3.416184971098266</v>
+        <v>0.9304347826086956</v>
       </c>
       <c r="M2">
-        <v>7.91</v>
+        <v>10.2</v>
       </c>
       <c r="N2">
-        <v>0.06363636363636364</v>
+        <v>0.08436724565756823</v>
       </c>
       <c r="O2">
-        <v>1.338409475465313</v>
+        <v>0.9532710280373832</v>
       </c>
       <c r="P2">
-        <v>7.91</v>
+        <v>7.96</v>
       </c>
       <c r="Q2">
-        <v>0.06363636363636364</v>
+        <v>0.06583953680727873</v>
       </c>
       <c r="R2">
-        <v>1.338409475465313</v>
+        <v>0.7439252336448599</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.239999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.2196078431372548</v>
       </c>
       <c r="U2">
-        <v>0.003</v>
+        <v>5.35</v>
       </c>
       <c r="V2">
-        <v>2.413515687851971e-05</v>
+        <v>0.04425144747725392</v>
+      </c>
+      <c r="W2">
+        <v>0.1931407942238267</v>
       </c>
       <c r="X2">
-        <v>0.0421964431165108</v>
+        <v>0.07998914383906056</v>
+      </c>
+      <c r="Y2">
+        <v>0.1131516503847662</v>
+      </c>
+      <c r="Z2">
+        <v>0.1935473012774122</v>
+      </c>
+      <c r="AA2">
+        <v>0.01363762857000835</v>
       </c>
       <c r="AB2">
-        <v>0.03872540146210753</v>
+        <v>0.07035892248540834</v>
+      </c>
+      <c r="AC2">
+        <v>-0.0567212939154</v>
       </c>
       <c r="AD2">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="AG2">
-        <v>45.697</v>
+        <v>39.25</v>
       </c>
       <c r="AH2">
-        <v>0.2688235294117647</v>
+        <v>0.2694864048338368</v>
       </c>
       <c r="AI2">
-        <v>0.4520276953511375</v>
+        <v>0.4076782449725777</v>
       </c>
       <c r="AJ2">
-        <v>0.2688106260698718</v>
+        <v>0.2450827349359975</v>
       </c>
       <c r="AK2">
-        <v>0.4520114345628456</v>
+        <v>0.3772224891878905</v>
       </c>
       <c r="AL2">
-        <v>0.277</v>
+        <v>1.16</v>
       </c>
       <c r="AM2">
-        <v>0.277</v>
+        <v>1.16</v>
       </c>
       <c r="AN2">
-        <v>-10.48165137614679</v>
+        <v>35.68</v>
       </c>
       <c r="AO2">
-        <v>-16.60649819494585</v>
+        <v>0.8413793103448276</v>
       </c>
       <c r="AP2">
-        <v>-10.48096330275229</v>
+        <v>31.4</v>
       </c>
       <c r="AQ2">
-        <v>-16.60649819494585</v>
+        <v>0.8413793103448276</v>
       </c>
     </row>
     <row r="3">
@@ -701,100 +716,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>-3.497109826589595</v>
+        <v>-0.3173913043478261</v>
       </c>
       <c r="H3">
-        <v>-3.497109826589595</v>
+        <v>-0.3173913043478261</v>
       </c>
       <c r="I3">
-        <v>-2.658959537572254</v>
+        <v>0.08486956521739131</v>
       </c>
       <c r="J3">
-        <v>-2.155617402887795</v>
+        <v>0.07046147623862488</v>
       </c>
       <c r="K3">
-        <v>5.91</v>
+        <v>10.7</v>
       </c>
       <c r="L3">
-        <v>3.416184971098266</v>
+        <v>0.9304347826086956</v>
       </c>
       <c r="M3">
-        <v>7.91</v>
+        <v>10.2</v>
       </c>
       <c r="N3">
-        <v>0.06363636363636364</v>
+        <v>0.08436724565756823</v>
       </c>
       <c r="O3">
-        <v>1.338409475465313</v>
+        <v>0.9532710280373832</v>
       </c>
       <c r="P3">
-        <v>7.91</v>
+        <v>7.96</v>
       </c>
       <c r="Q3">
-        <v>0.06363636363636364</v>
+        <v>0.06583953680727873</v>
       </c>
       <c r="R3">
-        <v>1.338409475465313</v>
+        <v>0.7439252336448599</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.239999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2196078431372548</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>5.35</v>
       </c>
       <c r="V3">
-        <v>2.413515687851971e-05</v>
+        <v>0.04425144747725392</v>
+      </c>
+      <c r="W3">
+        <v>0.1931407942238267</v>
       </c>
       <c r="X3">
-        <v>0.0421964431165108</v>
+        <v>0.07998914383906056</v>
+      </c>
+      <c r="Y3">
+        <v>0.1131516503847662</v>
+      </c>
+      <c r="Z3">
+        <v>0.1935473012774122</v>
+      </c>
+      <c r="AA3">
+        <v>0.01363762857000835</v>
       </c>
       <c r="AB3">
-        <v>0.03872540146210753</v>
+        <v>0.07035892248540834</v>
+      </c>
+      <c r="AC3">
+        <v>-0.0567212939154</v>
       </c>
       <c r="AD3">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="AG3">
-        <v>45.697</v>
+        <v>39.25</v>
       </c>
       <c r="AH3">
-        <v>0.2688235294117647</v>
+        <v>0.2694864048338368</v>
       </c>
       <c r="AI3">
-        <v>0.4520276953511375</v>
+        <v>0.4076782449725777</v>
       </c>
       <c r="AJ3">
-        <v>0.2688106260698718</v>
+        <v>0.2450827349359975</v>
       </c>
       <c r="AK3">
-        <v>0.4520114345628456</v>
+        <v>0.3772224891878905</v>
       </c>
       <c r="AL3">
-        <v>0.277</v>
+        <v>1.16</v>
       </c>
       <c r="AM3">
-        <v>0.277</v>
+        <v>1.16</v>
       </c>
       <c r="AN3">
-        <v>-10.48165137614679</v>
+        <v>35.68</v>
       </c>
       <c r="AO3">
-        <v>-16.60649819494585</v>
+        <v>0.8413793103448276</v>
       </c>
       <c r="AP3">
-        <v>-10.48096330275229</v>
+        <v>31.4</v>
       </c>
       <c r="AQ3">
-        <v>-16.60649819494585</v>
+        <v>0.8413793103448276</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/czech_republic/czech_republic_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_brokerage_investment_banking.xlsx
@@ -588,115 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.3173913043478261</v>
+        <v>0.5358090185676392</v>
       </c>
       <c r="H2">
-        <v>-0.3173913043478261</v>
+        <v>0.5358090185676392</v>
       </c>
       <c r="I2">
-        <v>0.08486956521739131</v>
+        <v>0.5411140583554376</v>
       </c>
       <c r="J2">
-        <v>0.07046147623862488</v>
+        <v>0.4200255977444306</v>
       </c>
       <c r="K2">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="L2">
-        <v>0.9304347826086956</v>
+        <v>0.2944297082228116</v>
       </c>
       <c r="M2">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="N2">
-        <v>0.08436724565756823</v>
+        <v>0.07320441988950276</v>
       </c>
       <c r="O2">
-        <v>0.9532710280373832</v>
+        <v>0.954954954954955</v>
       </c>
       <c r="P2">
-        <v>7.96</v>
+        <v>10.6</v>
       </c>
       <c r="Q2">
-        <v>0.06583953680727873</v>
+        <v>0.07320441988950276</v>
       </c>
       <c r="R2">
-        <v>0.7439252336448599</v>
+        <v>0.954954954954955</v>
       </c>
       <c r="S2">
-        <v>2.239999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2196078431372548</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.04425144747725392</v>
+        <v>0.4703038674033149</v>
       </c>
       <c r="W2">
-        <v>0.1931407942238267</v>
+        <v>0.1720930232558139</v>
       </c>
       <c r="X2">
-        <v>0.07998914383906056</v>
+        <v>0.06024886308651465</v>
       </c>
       <c r="Y2">
-        <v>0.1131516503847662</v>
+        <v>0.1118441601692993</v>
       </c>
       <c r="Z2">
-        <v>0.1935473012774122</v>
+        <v>0.3666387878552118</v>
       </c>
       <c r="AA2">
-        <v>0.01363762857000835</v>
+        <v>0.1539976760251788</v>
       </c>
       <c r="AB2">
-        <v>0.07035892248540834</v>
+        <v>0.06008452357744868</v>
       </c>
       <c r="AC2">
-        <v>-0.0567212939154</v>
+        <v>0.09391315244773013</v>
       </c>
       <c r="AD2">
-        <v>44.6</v>
+        <v>2.08</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>44.6</v>
+        <v>2.08</v>
       </c>
       <c r="AG2">
-        <v>39.25</v>
+        <v>-66.02</v>
       </c>
       <c r="AH2">
-        <v>0.2694864048338368</v>
+        <v>0.01416122004357298</v>
       </c>
       <c r="AI2">
-        <v>0.4076782449725777</v>
+        <v>0.02488633644412539</v>
       </c>
       <c r="AJ2">
-        <v>0.2450827349359975</v>
+        <v>-0.8380299568418378</v>
       </c>
       <c r="AK2">
-        <v>0.3772224891878905</v>
+        <v>-4.264857881136949</v>
       </c>
       <c r="AL2">
-        <v>1.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AM2">
-        <v>1.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AN2">
-        <v>35.68</v>
+        <v>0.0962962962962963</v>
       </c>
       <c r="AO2">
-        <v>0.8413793103448276</v>
+        <v>2.411347517730496</v>
       </c>
       <c r="AP2">
-        <v>31.4</v>
+        <v>-3.056481481481481</v>
       </c>
       <c r="AQ2">
-        <v>0.8413793103448276</v>
+        <v>2.411347517730496</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +716,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.3173913043478261</v>
+        <v>0.5358090185676392</v>
       </c>
       <c r="H3">
-        <v>-0.3173913043478261</v>
+        <v>0.5358090185676392</v>
       </c>
       <c r="I3">
-        <v>0.08486956521739131</v>
+        <v>0.5411140583554376</v>
       </c>
       <c r="J3">
-        <v>0.07046147623862488</v>
+        <v>0.4200255977444306</v>
       </c>
       <c r="K3">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="L3">
-        <v>0.9304347826086956</v>
+        <v>0.2944297082228116</v>
       </c>
       <c r="M3">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="N3">
-        <v>0.08436724565756823</v>
+        <v>0.07320441988950276</v>
       </c>
       <c r="O3">
-        <v>0.9532710280373832</v>
+        <v>0.954954954954955</v>
       </c>
       <c r="P3">
-        <v>7.96</v>
+        <v>10.6</v>
       </c>
       <c r="Q3">
-        <v>0.06583953680727873</v>
+        <v>0.07320441988950276</v>
       </c>
       <c r="R3">
-        <v>0.7439252336448599</v>
+        <v>0.954954954954955</v>
       </c>
       <c r="S3">
-        <v>2.239999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2196078431372548</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>5.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.04425144747725392</v>
+        <v>0.4703038674033149</v>
       </c>
       <c r="W3">
-        <v>0.1931407942238267</v>
+        <v>0.1720930232558139</v>
       </c>
       <c r="X3">
-        <v>0.07998914383906056</v>
+        <v>0.06024886308651465</v>
       </c>
       <c r="Y3">
-        <v>0.1131516503847662</v>
+        <v>0.1118441601692993</v>
       </c>
       <c r="Z3">
-        <v>0.1935473012774122</v>
+        <v>0.3666387878552118</v>
       </c>
       <c r="AA3">
-        <v>0.01363762857000835</v>
+        <v>0.1539976760251788</v>
       </c>
       <c r="AB3">
-        <v>0.07035892248540834</v>
+        <v>0.06008452357744868</v>
       </c>
       <c r="AC3">
-        <v>-0.0567212939154</v>
+        <v>0.09391315244773013</v>
       </c>
       <c r="AD3">
-        <v>44.6</v>
+        <v>2.08</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>44.6</v>
+        <v>2.08</v>
       </c>
       <c r="AG3">
-        <v>39.25</v>
+        <v>-66.02</v>
       </c>
       <c r="AH3">
-        <v>0.2694864048338368</v>
+        <v>0.01416122004357298</v>
       </c>
       <c r="AI3">
-        <v>0.4076782449725777</v>
+        <v>0.02488633644412539</v>
       </c>
       <c r="AJ3">
-        <v>0.2450827349359975</v>
+        <v>-0.8380299568418378</v>
       </c>
       <c r="AK3">
-        <v>0.3772224891878905</v>
+        <v>-4.264857881136949</v>
       </c>
       <c r="AL3">
-        <v>1.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AM3">
-        <v>1.16</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AN3">
-        <v>35.68</v>
+        <v>0.0962962962962963</v>
       </c>
       <c r="AO3">
-        <v>0.8413793103448276</v>
+        <v>2.411347517730496</v>
       </c>
       <c r="AP3">
-        <v>31.4</v>
+        <v>-3.056481481481481</v>
       </c>
       <c r="AQ3">
-        <v>0.8413793103448276</v>
+        <v>2.411347517730496</v>
       </c>
     </row>
   </sheetData>
